--- a/output/看屋檢查清單_新北建案_2026-08-23.xlsx
+++ b/output/看屋檢查清單_新北建案_2026-08-23.xlsx
@@ -520,7 +520,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>資料搜尋日期：2026-08-22　|　來源：591新建案、591實價登錄、樂居、住展、樂屋網、5168比價王、甲山林集團官網、PLEX</t>
+          <t>資料搜尋日期：2026-08-23　|　來源：591新建案／實價登錄、樂居、樂屋網、5168、住展、永慶、信義、PLEX、甲山林官網、Mobile01、看屋部落格　|　共用說明：①貸款試算＝貸8成/30年/利率2.5%（2026年五大行庫2.3~2.6%）；新青安3.0首購約1.775%、上限1,000萬 ②稅費＝契稅(房屋評定現值×6%)＋印花稅0.1%＋代書費1.5~2萬＋規費0.1%，概估總價1~1.5% ③預售屋法定保固：結構15年、固定建材設備1年，自交屋日起算 ④預售屋履約保證五擇一：價金返還保證／價金信託／不動產開發信託／同業連帶擔保／公會連帶保證 ⑤斷層：台北盆地列冊活動斷層僅山腳斷層(第二類，約1萬年前活動)，位於盆地西北側樹林—北投—金山一線 ⑥土壤液化查詢：新北 liquid.net.tw/NewTaipei、台北 liquid.net.tw/cgs/Web/Map.aspx</t>
         </is>
       </c>
     </row>
@@ -546,35 +546,35 @@
         <is>
           <t>敦南之森
 新北市新店區永安街45號
-安康輕軌新和國小站(步行約4分鐘)</t>
+安坑輕軌新和國小站(步行約4分鐘)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
           <t>新濠漾
-新北市三重區頂文路2-2號
-未知待查詢</t>
+新北市三重區頂文路1號／2-2號
+三重站(機捷+中和新蘆線)步行約13分鐘</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>新濠岳
-新北市土城區中央路四段125巷、福田路交叉口
-未知待查詢</t>
+新北市土城區中央路四段125巷、福田路口
+板南線頂埔站約650公尺(步行9分鐘)</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
           <t>汐止星野之森
-新北市汐止區新台五路二段238巷1號旁（A~G全區）
-無捷運，鄰台鐵汐科/汐止站(距離待確認)</t>
+新北市汐止區新台五路二段238巷(A~G全區)
+無捷運，社區接駁車往返汐科站/南港展覽館</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
           <t>文德好境
-台北市內湖區陽光街101號一帶
-捷運文德站約650公尺</t>
+台北市內湖區陽光街161巷12號(另載101號)
+捷運文德站約650公尺(步行約7分鐘)</t>
         </is>
       </c>
     </row>
@@ -604,17 +604,17 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>新濠漾</t>
+          <t>新濠漾（同系列另有II紐約公園、III巴黎公園、4英倫公園）</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>新濠岳</t>
+          <t>新濠岳（土城運校重劃區）</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>汐止星野之森（A~G 全區，看屋範圍：1房為主、最多2房）</t>
+          <t>汐止星野之森（A~G全區，看屋範圍：1房為主、最多2房）</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>新北市板橋區民生路三段188號</t>
+          <t>新北市板橋區民生路三段188號（門牌另見186號25樓之2等）</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -642,22 +642,23 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>新北市三重區頂文路2-2號</t>
+          <t>新北市三重區頂文路1號（另載2-2號）</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>新北市土城區中央路四段125巷、福田路交叉口（先前備註猜測為三重／蘆洲，經搜尋確認為土城區，已更正）</t>
+          <t>新北市土城區中央路四段125巷、福田路交叉口</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>新北市汐止區新台五路二段238巷1號旁（全案分A/B/C/D/E/G區）</t>
+          <t>新北市汐止區新台五路二段238巷
+B區22號、D區31號、G區1號旁；A/C/E區同街廓</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>台北市內湖區陽光街101號一帶（一說陽光街161巷12號，門牌需現場確認）</t>
+          <t>台北市內湖區陽光街161巷12號（另有來源記為陽光街101號，門牌以謄本為準）</t>
         </is>
       </c>
     </row>
@@ -708,7 +709,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>安鋒建設／宏昌興業</t>
+          <t>安豊集團（部分來源記為安鋒建設／宏昌興業）</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -728,7 +729,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>明緯建設、白天鵝建設、久郡建設等共同開發（甲山林集團行銷）</t>
+          <t>明緯建設、白天鵝建設、久郡建設等共同開發</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -749,9 +750,9 @@
           <t>海悅廣告</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>家河建築行銷團隊（JIAHE）</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -769,9 +770,9 @@
           <t>甲山林集團</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢（目前多為房仲轉售之新古屋物件）</t>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>已完工社區，目前多為房仲轉售之新古屋物件（約6戶銷售中）</t>
         </is>
       </c>
     </row>
@@ -789,7 +790,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>約1,262坪</t>
+          <t>約1,262.47坪</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -805,7 +806,7 @@
       <c r="G10" s="8" t="inlineStr">
         <is>
           <t>全案開發面積約4,800坪
-B區未知待查詢、D區約1,783坪、G區781.52坪（建蔽率40.8%）</t>
+D區約1,783坪、G區781.52坪（建蔽率40.8%）</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
@@ -823,38 +824,41 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>2棟，地上26層、地下5層，共323戶</t>
+          <t>2棟，地上26層、地下5層
+共322~323戶住家</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>地上13層、地下5層，共400戶</t>
+          <t>A、B兩棟，地上13層、地下5層
+共400戶</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>2棟，地上23層、地下5層，共396戶純住家</t>
+          <t>2棟，地上23層、地下5層
+共396戶純住家（無店面）</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>3棟，地上17、18層、地下5層，共661戶</t>
+          <t>3棟，地上17、18層、地下5層
+共661戶</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>B區：地上11層/地下4層，262戶+5店面
-D區：地上11層/地下4層，351戶
-G區：地上11層/地下5層，155戶+5店面
-A區：地上11層/地下3層
-C區：地上11層/地下4層
-E區為共用公設大樓</t>
+          <t>B區262戶+5店面（地上11/地下4）
+D區351戶（地上11/地下4）
+G區155戶+5店面（地上11/地下5）
+A區地上11/地下3、C區地上11/地下4
+E區為全案共用公設大樓</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
           <t>共196戶
-A、B、C棟地上5層/地下1~2層，E棟地上3層/地下1層
+A、B、C棟地上5層/地下1~2層；E棟地上3層/地下1層
 A、B棟每層14~15戶配2部電梯；C棟每層8戶配1部電梯</t>
         </is>
       </c>
@@ -873,7 +877,8 @@
               <color rgb="FF000000"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">套房~3房
+            <t xml:space="preserve">套房~3房，全案12~32坪
+【看屋重點】套房12坪、1+1房15坪
 </t>
           </r>
           <r>
@@ -890,27 +895,493 @@
         <is>
           <r>
             <rPr>
-              <b val="1"/>
-              <color rgb="001F4E78"/>
+              <color rgb="FF000000"/>
               <sz val="10"/>
             </rPr>
-            <t>1~3房，16~32坪</t>
+            <t xml:space="preserve">1~3房，全案16~32坪
+【看屋重點】1房16/17/18坪
+</t>
           </r>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
           <r>
             <rPr>
               <b val="1"/>
               <color rgb="001F4E78"/>
               <sz val="10"/>
             </rPr>
-            <t>1~3房，21.79~42.63坪</t>
+            <t>2房24坪、3房32坪</t>
           </r>
         </is>
       </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">1~3房，全案21.79~42.63坪
+【看屋重點】1房約21.79坪起
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="001F4E78"/>
+              <sz val="10"/>
+            </rPr>
+            <t>2房、3房最大至42.63坪</t>
+          </r>
+        </is>
+      </c>
       <c r="F12" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">1~3房，全案12~29坪
+【看屋重點】1房12~15坪、1+1房17~18坪
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="001F4E78"/>
+              <sz val="10"/>
+            </rPr>
+            <t>2房20~23坪、2+1房23坪、3房26~29坪</t>
+          </r>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">分期：B區一期、G區二期、D區三期、A/C區四期、E區公設樓
+【符合看屋範圍】B區1房20坪(另有18坪)、2房23坪；G區1+1房20~22坪、2房25坪；D區2房20/25/26/27坪
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="001F4E78"/>
+              <sz val="10"/>
+            </rPr>
+            <t>【超出範圍】B區3房41.2坪、D區3房32~38坪及4房41坪、G區3房35/41坪及4房43/47坪、C區26~39坪、A區最大42坪</t>
+          </r>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">【看屋範圍】1房12坪、14坪、18坪、19坪（1+1房約18坪）
+主力為12坪與18坪
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="001F4E78"/>
+              <sz val="10"/>
+            </rPr>
+            <t>【超出範圍】2房21/27/29坪、3房33/37坪，不列入看屋</t>
+          </r>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>二、建商與代銷背景</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>建商過往作品</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>未知待查詢</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>茂德建設於新店區已有推案紀錄，本案為再度推案
+具體案名未知待查詢</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>新濠建設：三重新濠漾系列（II紐約公園、III巴黎公園、4英倫公園）、土城新濠岳</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>新濠建設：三重新濠漾系列（I~4期）</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>未知待查詢</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>瓏山林企業：國內知名建商，另有瓏山林系列住宅與飯店事業
+具體案名未知待查詢</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>建商財務／信用評價</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>未知待查詢</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>未知待查詢</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>未知待查詢</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>未知待查詢</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>未知待查詢</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>未知待查詢</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>建商是否有糾紛或訴訟紀錄</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>未知待查詢</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>未知待查詢</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>未知待查詢</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>未知待查詢</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>未知待查詢</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>未知待查詢</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>代銷公司背景</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>海悅廣告：國內大型代銷公司，官網設有本案專屬建案頁</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>家河建築行銷團隊，官網設有本案專頁</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>未知待查詢</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>未知待查詢</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>甲山林集團：國內大型代銷/建設集團，官網有本案專頁（主打首付58萬起）</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>已完工，非代銷銷售；由房仲轉售</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>保固條款（結構／防水年限）</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>已完工，結構保固自首次交屋日起算15年、設備1年（多已屆滿）
+另有民法瑕疵擔保：發現後6個月內、交屋5年內</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>預售屋法定保固（見表尾說明）</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>已完工，結構保固自首次交屋日起算15年、設備1年（多已屆滿）
+另有民法瑕疵擔保：發現後6個月內、交屋5年內</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>預售屋法定保固（見表尾說明）</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>預售屋法定保固（見表尾說明）
+本案分期推出，已完工分區（B/D/G等）保固多已起算，需依各區使照日期推算</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>已完工，結構保固自首次交屋日起算15年、設備1年（多已屆滿）
+另有民法瑕疵擔保：發現後6個月內、交屋5年內</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>履約保證方式</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>成屋履約保證專戶（建經公司價金信託），房仲成交一般均有提供</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>預售屋法定五擇一（見表尾說明）
+⚠️簽約前務必索取履保文件確認採哪一種</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>成屋履約保證專戶（建經公司價金信託），房仲成交一般均有提供</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>預售屋法定五擇一（見表尾說明）
+⚠️簽約前務必索取履保文件確認採哪一種</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>預售屋法定五擇一（見表尾說明）
+⚠️簽約前務必索取履保文件確認採哪一種
+已完工分區之轉售戶則適用成屋履約保證</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>成屋履約保證專戶（建經公司價金信託），房仲成交一般均有提供</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>客戶評價／網路口碑</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Mobile01 討論串評價分歧：
+優點－大廳鍍鈦/大板磚/石材、陽台多且大、落地窗隔音佳
+缺點－新埔5號出口一帶商家少覓食不便、高架橋噪音明顯</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>樂居、中時房產、林保宏等看屋筆記均有專文分析
+主打小坪數低總價帶產品</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>業界首創「律師見證不二價」銷售
+優點：純住家中型社區、住戶單純、綠覆率高、街道整齊
+缺點：周邊生活機能未成熟、鄰近仍有不少中小型工廠</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>多篇看屋部落格與Mobile01討論
+正評：國家級四大標章、樓高3米6、千坪基地北歐泳池會所、小坪數低總價
+已購戶回饋：有客變諮詢活動與工程進度報告</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>Mobile01 討論串評價分歧
+主要疑慮：山坡地旁有夜總會（墓地）、濕氣重
+優點：總價低、社區接駁車、日系設計（G區由 NONSCALE 設計）</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>591開箱文、樂居看屋筆記、Mobile01與果仁家均有討論
+正評：一卡皮箱入住（附裝潢家電）、北市門牌千萬內、低密度5層社區
+負評：公設比39%偏高、機械車位、單層戶數多</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>三、產品規劃與坪數</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>各房型權狀坪數區間</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">套房12坪、1+1房15坪
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="001F4E78"/>
+              <sz val="10"/>
+            </rPr>
+            <t>2房18~28坪、3房30~32坪</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+全案坪數區間12~32坪</t>
+          </r>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">1房16坪、17坪、18坪
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="001F4E78"/>
+              <sz val="10"/>
+            </rPr>
+            <t>2房24坪、3房32坪</t>
+          </r>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">全案1~3房21.79~42.63坪
+</t>
+          </r>
+          <r>
+            <rPr>
+              <b val="1"/>
+              <color rgb="001F4E78"/>
+              <sz val="10"/>
+            </rPr>
+            <t>2~3房佔多數，本案最小戶即21.79坪</t>
+          </r>
+          <r>
+            <rPr>
+              <color rgb="FF000000"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">
+（各房型細分坪數需向代銷索取平面圖）</t>
+          </r>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -930,427 +1401,20 @@
           </r>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">分期：B區第一期、G區第二期、D區第三期、A/C區第四期、E區公設樓
-【符合看屋範圍】B區1房20坪、2房23坪、另有18坪；G區1+1房20~22坪、2房25坪
-</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="001F4E78"/>
-              <sz val="10"/>
-            </rPr>
-            <t>【超出範圍】B區3房41.2坪、G區3房35/41坪及4房43/47坪、C區26~39坪、D區20~41坪、A區18~42坪，3房以上不列入看屋</t>
-          </r>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">【看屋範圍】1房（套房型）12、14、18、19坪，社區以12坪與18坪為主力
-</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="001F4E78"/>
-              <sz val="10"/>
-            </rPr>
-            <t>【超出範圍】2房21/27/29坪、3房37坪，不列入看屋</t>
-          </r>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>二、建商與代銷背景</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>建商過往作品</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>建商財務／信用評價</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>建商是否有糾紛或訴訟紀錄</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>代銷公司背景</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>保固條款（結構／防水年限）</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>履約保證方式</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>客戶評價／網路口碑</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>三、產品規劃與坪數</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>各房型權狀坪數區間</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">套房12坪、1+1房15坪
-</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="001F4E78"/>
-              <sz val="10"/>
-            </rPr>
-            <t>2房18~28坪、3房30~32坪</t>
-          </r>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="001F4E78"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1房、2房、3房：16~32坪</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>（各房型細分坪數區間未知待查詢）</t>
-          </r>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="001F4E78"/>
-              <sz val="10"/>
-            </rPr>
-            <t>1房、2房、3房：21.79~42.63坪</t>
-          </r>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t>（各房型細分坪數區間未知待查詢）</t>
-          </r>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <color rgb="FF000000"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">1房12~15坪、1+1房17~18坪
-</t>
-          </r>
-          <r>
-            <rPr>
-              <b val="1"/>
-              <color rgb="001F4E78"/>
-              <sz val="10"/>
-            </rPr>
-            <t>2房20~23坪、2+1房23坪、3房26~29坪</t>
-          </r>
-        </is>
-      </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
           <t>【看屋範圍內】
 B區：18坪、1房20坪、2房23坪
+D區：2房20/25/26/27坪
 G區：1+1房20~22坪、2房25坪
-A區：18坪起（1~2房細分坪數未知待查詢）
-C區：最小26坪，恐無1~2房產品，需向代銷確認
-D區：最小20坪（1~2房細分坪數未知待查詢）</t>
+A區：18坪起（1~3房，18~42坪）
+C區：最小26坪，恐無1~2房產品，需向代銷確認</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
           <t>【看屋範圍】1房12坪、14坪、18坪、19坪
-（12坪為最小主力產品，18~19坪為1房大坪數）</t>
+（12坪為最小主力，18~19坪為1房大坪數／1+1房）</t>
         </is>
       </c>
     </row>
@@ -1361,9 +1425,9 @@
           <t>主建物／附屬建物／公設比例</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>公設比約39.96%（偏高，小坪數實際使用空間需現場確認）</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -1390,7 +1454,8 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>公設比約39%（偏高，小坪數實際使用空間需現場確認）</t>
+          <t>公設比約39%（偏高）
+12坪產品扣除公設後實際使用空間有限，務必現場丈量</t>
         </is>
       </c>
     </row>
@@ -1401,19 +1466,20 @@
           <t>公設項目與內容</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>健身房、舞蹈教室、KTV
+B1設有可冷藏之垃圾資源回收設備</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>（以未來管委會決議為主）挑高六米大面窗接待大廳、日系藏書閣、音樂教室、健身房、KTV、兒童遊戲區、廚藝教室、茶屋、瑜珈教室、外送暫存區</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>接待大廳、中庭花園、空中花園、交誼廳、會議室、閱覽室、視聽室、健身房、親子遊戲區、兒童遊戲區、KTV、俱樂部、瑜伽教室、廚藝教室</t>
+          <t>接待大廳、中庭花園、空中花園、交誼廳、會議室、閱覽室、視聽室、曬被區、健身房、親子遊戲區、兒童遊戲區、KTV、Lounge Bar、俱樂部、瑜伽教室、廚藝教室、宴會廳</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -1423,14 +1489,16 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>B區（公設多集中1F）：接待大廳、庭園、交誼廳、閱覽室、媽媽教室、音樂教室、健身房、宴會廳、戶外烤肉區
-G區：主打共享生活居所、全齡公共設施（遠端工作/休憩養生空間）
+          <t>B區（多集中1F）：接待大廳、庭園、交誼廳、閱覽室、媽媽教室、音樂教室、健身房、宴會廳、戶外烤肉區
+G區：共享生活居所、全齡公共設施（遠端工作/休憩養生空間）
 E區為全案共用公設大樓</t>
         </is>
       </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>屋頂花園、接待大廳、信箱區
+B1為社區入口與機車停放區
+公設項目相對精簡（低樓層社區）</t>
         </is>
       </c>
     </row>
@@ -1443,35 +1511,41 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>坡道平面57個＋機械59個，價格未知待查詢</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+          <t>坡道平面57個＋機械59個
+車位價格未知待查詢（需向代銷確認平面/機械價差）</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>平面式車位284個
+B1另設10台社區共享電動機車供住戶短程代步
+車位價格未知待查詢</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>坡道平面車位309個，價格未知待查詢</t>
+          <t>坡道平面式車位309個（全平面，無機械）
+車位價格未知待查詢</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>平面式604個，價格未知待查詢</t>
+          <t>平面式車位604個（全平面）
+實登多筆為「無車位」交易，車位可單獨計價，價格未知待查詢</t>
         </is>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>B區：坡道平面式107個（車道由新台五路238巷進出，獨立式車道不影響上方住戶）
+          <t>B區：坡道平面式107個（車道由新台五路238巷進出，獨立車道不影響上方住戶）
 G區：平面式112個
 其他分區與車位價格未知待查詢</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>機械車位86個，車位價格約150萬元
-（機械車位對車輛尺寸有限制，需確認可停車型）</t>
+          <t>機械停車塔86個（位於社區入口附近）
+車位價格約150萬元
+機械式對車輛長寬高有限制，需確認可停車型</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1578,13 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>A區地上11層/地下3層；B區地上11層/地下4層；C區地上11層/地下4層；D區地上11層/地下4層；G區地上11層/地下5層</t>
+          <t>A區地上11/地下3；B區地上11/地下4；C區地上11/地下4；D區地上11/地下4；G區地上11/地下5</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>A/B/C棟地上5層、地下1~2層；E棟地上3層、地下1層（低樓層華廈型）</t>
+          <t>A/B/C棟地上5層、地下1~2層；E棟地上3層、地下1層
+低樓層低密度華廈型</t>
         </is>
       </c>
     </row>
@@ -1520,14 +1595,18 @@
           <t>建材設備（廚具、衛浴、電梯品牌）</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>衛浴臉盆：Villeroy &amp; Boch
+大廳建材：鍍鈦、大板磚、石材
+落地窗隔音表現受住戶好評
+廚具與電梯品牌未知待查詢</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>報導稱工法建材較前案「與時俱進」，但未列明品牌
+未知待查詢</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -1535,20 +1614,24 @@
           <t>未知待查詢</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢
-（G區由安藤忠雄御用設計團隊 NONSCALE 設計，主打日系建築）</t>
-        </is>
-      </c>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢（主打「裝潢家電全附、一卡皮箱即可入住」）</t>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>申請國家級四大標章：鑽石級綠建築、六級抗震耐震標章等
+室內樓高3米6
+廚具/衛浴/電梯品牌未知待查詢</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>G區由安藤忠雄御用設計團隊 NONSCALE 設計，主打日系建築
+D區結構為鋼筋混凝土（RC）
+廚具/衛浴/電梯品牌未知待查詢</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>主打「裝潢家電全附、一卡皮箱即可入住」
+具體品牌未知待查詢（中古轉售戶之裝潢狀況因戶而異）</t>
         </is>
       </c>
     </row>
@@ -1559,9 +1642,10 @@
           <t>格局方正度／採光通風</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>陽台配置多且大，部分戶型有豪華陽台設定
+實際方正度需看平面圖現場確認</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
@@ -1569,26 +1653,28 @@
           <t>未知待查詢</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>河岸景觀宅訴求，千坪花園中庭
+實際採光面需依棟別與樓層確認</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>樓高3米6有利空間感與通風
+實際方正度需依平面圖確認</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>B區標準層1樓面24戶搭配3部電梯（戶數偏多，需現場確認採光與電梯等候）
-其他分區未知待查詢</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢
-（A/B棟單層14~15戶配2部電梯，戶數密度偏高，需現場確認1房採光面與通風）</t>
+          <t>B區標準層1樓面24戶搭配3部電梯（戶數密度高，需確認採光面與電梯等候）
+網友反映區域濕氣偏重，通風與除濕需重點檢視</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>A/B棟單層14~15戶配2部電梯，戶數密度偏高
+1房產品採光面與通風需逐戶現場確認</t>
         </is>
       </c>
     </row>
@@ -1652,9 +1738,10 @@
           <t>未知待查詢</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>銷售期間提供室內設計師客變建議活動
+建造期間提供工程進度報告，交屋後有一對一諮詢服務</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr">
@@ -1664,7 +1751,8 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>已完工新古屋，附裝潢與家電；客變不適用</t>
+          <t>已完工新古屋，附裝潢與家電；不適用客變
+交屋現況以買賣契約與現場點交為準</t>
         </is>
       </c>
     </row>
@@ -1684,32 +1772,39 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>環狀線新埔民生站，步行約350公尺(約5分鐘)</t>
+          <t>環狀線新埔民生站約350公尺（步行約5分鐘）
+可快速串聯板南線與環狀線（雙捷交匯）</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>安康輕軌新和國小站(步行約4分鐘)，另近南勢角站(約10分鐘)、景平站</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢（汐止無捷運，主要靠台鐵汐科/汐止站與公車，實際距離待查）</t>
+          <t>安坑輕軌新和國小站步行約4分鐘
+捷運南勢角站步行約10~12分鐘
+另近景平站；輕軌約2分鐘可達十四張站</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>步行約13分鐘至三重站（機場捷運＋中和新蘆線雙捷）
+（此距離為同系列巴黎公園資料，本案實際距離需現場確認）</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>板南線頂埔站約650公尺（步行約9分鐘）
+三鶯線2025年通車後可由頂埔站往三峽、鶯歌</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>無捷運。位於新台五路旁，社區備有接駁車往返南港展覽館與遠雄U-TOWN（汐科站）
+車行約15分鐘到南港</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>捷運文湖線文德站約650公尺（步行約8~10分鐘）</t>
+          <t>捷運文湖線文德站約650公尺（步行約7分鐘）
+紫陽公車站步行約2分鐘</t>
         </is>
       </c>
     </row>
@@ -1740,14 +1835,15 @@
           <t>未知待查詢</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>社區接駁車每日往返南港展覽館及汐科站
+一般公車路線班次未知待查詢</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>紫陽站（步行約2分鐘），路線與班次未知待查詢</t>
         </is>
       </c>
     </row>
@@ -1758,24 +1854,27 @@
           <t>鄰近學區（國小／國中）</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>板橋區學區依戶籍里別劃分，鄰近有新埔國小、埔墘國小
+⚠️確切學區以新北市板橋區公所公告之「板橋區國小/國中學區一覽表」為準，需以實際門牌所屬里別查詢</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>新北市新店區新和國民小學（步行約6分鐘）
+國中學區未知待查詢</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>興穀國小（步行約9分鐘）
+三重國中（車程約8分鐘）</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>頂埔國小、土城國中</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -1783,9 +1882,10 @@
           <t>未知待查詢</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>內湖國小、內湖國中
+另近內湖高中、文德女中（實際學區以戶籍地劃分為準，需向區公所確認）</t>
         </is>
       </c>
     </row>
@@ -1796,34 +1896,43 @@
           <t>鄰近市場／超市／賣場</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>長江路至新海路一帶超商、超市
+裕民街傳統市場
+（部分住戶反映建案正對面商家較少）</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>鄰近敦南商圈、京站IKEA、新店裕隆城、新和商圈、南勢角商圈、景新市場</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+          <t>新和商圈（步行約6分）、南勢角商圈、景新市場
+敦南商圈、京站IKEA、新店裕隆城</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>三重家樂福、新莊IKEA、佳瑪商圈、宏匯廣場，均約車程10分鐘
+舊市區採買需車程約4分鐘</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>福誠街黃昏市場（可步行）
+全聯約600公尺、大潤發土城店騎車約5分鐘
+中央路四段兩側餐飲密集；土城交流道旁有大型賣場（車程5分）</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>南港CITYLINK、好市多、家樂福（車程可及）
+中信金融商圈、南港展覽館、流行音樂中心</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>步行不到2分鐘有便利商店；鄰內湖科學園區生活圈、書店商圈</t>
+          <t>步行不到2分鐘有便利商店
+蔦屋書店內湖店、CITY LINK 騎車約5分鐘
+鄰內湖科學園區生活圈</t>
         </is>
       </c>
     </row>
@@ -1841,17 +1950,19 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>鄰近天山公園、景新公園</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+          <t>天山公園、景新公園</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>鄰新北大都會公園（同系列建案主打）
+本案千坪中庭花園</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>社區千坪基地含中庭與空中花園
+周邊公園未知待查詢</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr">
@@ -1892,9 +2003,10 @@
           <t>未知待查詢</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>汐止國泰綜合醫院（新北市汐止區建成路59巷2號，區域級綜合醫院）
+實際車程距離需以基地座標實測</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
@@ -1915,24 +2027,27 @@
           <t>未知待查詢</t>
         </is>
       </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>十四張捷運聯合開發案（約4.3萬坪），與安坑輕軌十四張站出入口共構
+規劃水岸綠地、商場、智慧辦公室與住宅，為新店大規模指標開發案</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>西側為頭前重劃區與新莊副都心發展帶</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>捷運三鶯線（2025通車）
+鄰近土城科技園區、運校重劃區持續開發</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>基隆捷運（民生汐止線）已進入環評
+基地距保長坑2號站預定地（茄福街與茄東路口）約350公尺，為主要增值題材</t>
         </is>
       </c>
       <c r="H38" s="9" t="inlineStr">
@@ -1948,34 +2063,40 @@
           <t>生活機能綜合評分</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="H39" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢（近內科上班族商圈，機能佳但需實地確認）</t>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>中上：雙捷交匯、緊鄰新埔成熟商圈
+但新埔5號出口周邊店家較少，日常覓食需步行較遠</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>中上：三捷運線（中和新蘆線、環狀線、安坑輕軌）交會區
+生活圈成熟，另有十四張聯開案題材</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>中等：重劃區型純住宅，社區內公設完整
+但步行可及的日常機能仍在養成期，多需車程</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>中上：步行9分到捷運、黃昏市場與全聯可步行
+受惠周邊廠辦，餐飲密集</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>中下偏中：仰賴車行與接駁車，步行機能有限
+主要生活圈依附南港，捷運題材尚未落實</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>佳：北市內科生活圈，捷運、公車、書店商圈、公園、學區皆具
+為六案中生活機能最成熟者</t>
         </is>
       </c>
     </row>
@@ -1993,9 +2114,10 @@
           <t>鄰近嫌惡設施（殯儀館、垃圾場、高壓電塔等）</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>高架橋（大漢橋一帶）噪音為住戶主要抱怨點
+其他嫌惡設施未知待查詢</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
@@ -2003,19 +2125,20 @@
           <t>未知待查詢</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>周邊仍有不少中小型工廠營運（需現場確認氣味/噪音影響）</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>周邊廠辦林立（土城科技園區一帶），需現場確認實際影響</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>網友指出山坡地旁有夜總會（墓地），為主要嫌惡設施疑慮
+建議現場實地確認可視範圍與距離</t>
         </is>
       </c>
       <c r="H41" s="9" t="inlineStr">
@@ -2033,7 +2156,8 @@
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>未知待查詢</t>
+          <t>未知待查詢
+可至新北市土壤液化/防災圖台與國土測繪圖台查詢基地座標</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
@@ -2043,7 +2167,8 @@
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>未知待查詢</t>
+          <t>未知待查詢
+三重屬淡水河系低地，務必查詢基地淹水潛勢圖與確認社區防水閘門配置</t>
         </is>
       </c>
       <c r="F42" s="9" t="inlineStr">
@@ -2053,12 +2178,14 @@
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>未知待查詢（汐止歷史上為淹水熱區，務必查詢國土測繪圖台淹水潛勢圖並向代銷確認基地墊高）</t>
+          <t>未知待查詢
+汐止為歷史淹水熱區，務必查詢基地淹水潛勢圖、確認基地墊高與地下室防水閘門</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>未知待查詢</t>
+          <t>未知待查詢
+內湖部分區域屬基隆河沿岸，建議查詢台北市防災資訊網淹水潛勢圖</t>
         </is>
       </c>
     </row>
@@ -2071,32 +2198,38 @@
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>未知待查詢</t>
+          <t>未知待查詢
+板橋屬新北第1期已公布中級潛勢圖資（見表尾說明）確切基地</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>未知待查詢</t>
+          <t>未知待查詢
+新店屬新北第2期已公布中級潛勢圖資（見表尾說明）</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
-          <t>未知待查詢</t>
+          <t>未知待查詢
+三重屬新北第1期已公布中級潛勢圖資（見表尾說明）</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>未知待查詢</t>
+          <t>未知待查詢
+土城屬新北第2期已公布中級潛勢圖資（見表尾說明）</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
-          <t>未知待查詢</t>
+          <t>未知待查詢
+汐止屬新北第2期已公布中級潛勢圖資（見表尾說明）</t>
         </is>
       </c>
       <c r="H43" s="9" t="inlineStr">
         <is>
-          <t>未知待查詢</t>
+          <t>未知待查詢
+台北市已公布土壤液化潛勢圖資（見表尾說明）</t>
         </is>
       </c>
     </row>
@@ -2107,34 +2240,34 @@
           <t>是否位於斷層帶</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="G44" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="H44" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>板橋位於盆地內、不在山腳斷層線上，但距盆地西緣較近</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>新店位於盆地東南緣，不在山腳斷層線上</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>三重位於盆地西側，斷層跡經蘆洲—關渡一帶，距三重不遠，建議逐筆確認</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>土城位於盆地西南緣，不在山腳斷層線上</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>汐止位於盆地東側外緣丘陵帶，不在山腳斷層線上；惟屬山坡地，另需注意邊坡穩定</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>內湖位於盆地東北側，不在山腳斷層線上</t>
         </is>
       </c>
     </row>
@@ -2145,9 +2278,10 @@
           <t>噪音來源（鐵路／快速道路／工廠）</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>鄰近高架橋，車流噪音為已知問題
+落地窗隔音有做但仍建議現場開窗實測</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -2155,19 +2289,20 @@
           <t>未知待查詢</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F45" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="G45" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢（鄰新台五路主幹道，車流噪音需現場確認）</t>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>周邊中小型工廠為主要疑慮來源</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>鄰近中央路四段主幹道與廠辦區，需現場確認</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>鄰新台五路主幹道，車流噪音需現場確認
+近中山高、北二高、北宜高、環東快速道路交會帶</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr">
@@ -2193,9 +2328,9 @@
           <t>未知待查詢</t>
         </is>
       </c>
-      <c r="E46" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>純住家無店面規劃，住戶出入相對單純</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
@@ -2208,9 +2343,9 @@
           <t>未知待查詢</t>
         </is>
       </c>
-      <c r="H46" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>管理公司提供24小時飯店式管理</t>
         </is>
       </c>
     </row>
@@ -2223,39 +2358,51 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>591實價登錄：170筆成交，均價約76萬/坪</t>
+          <t>591：170筆成交，均價約76萬/坪
+5168：326筆實登，成交總價575~5,730萬，單價75~88萬/坪
+樂屋網：170筆，均價約73.7萬/坪</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>尚未開賣／預售初期，5168查詢暫無成交紀錄，未知待查詢</t>
+          <t>591：163筆實登，最新成交年月為2026年5月（民國115年）
+樂居：近一年均價約66.97萬/坪
+（本案仍在預售階段，實登筆數持續累積中）</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>591實價登錄：554筆成交，均價約67萬/坪</t>
+          <t>591：554筆成交，均價約67萬/坪
+樂居：近一年均價65.69萬/坪（301筆）
+樂屋網：596筆，均價約66萬/坪
+5168：均價約67.9萬/坪
+成交總價區間544~3,000萬；最新約66.3萬/坪</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>591實價登錄：329筆成交，均價約75萬/坪</t>
+          <t>591：329筆成交，均價約75萬/坪
+樂屋網：335筆均價79.7萬／246筆均價76.5萬
+樂居：近一年均價76.6萬/坪
+實例：2房20.7坪 單價73.9萬 總價1,526萬（無車位）；2房20.5坪 單價74.5萬 總價1,529萬（無車位）</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>各分區均價（591/5168/樂居）：
-A區約41~44萬/坪（51筆，總價600~2,390萬）
-B區約44~47萬/坪（362筆）
-C區約42~43萬/坪（173筆，總價1,060~2,270萬）
-D區約44.8~45萬/坪（628筆）
-G區約40~45萬/坪（171筆，開價45~48萬/坪）</t>
+          <t>A區：51筆，均價約41萬/坪（單價約44萬，總價600~2,390萬）
+B區：362筆，均價約46萬/坪；樂居近一年46.89萬（195筆）
+C區：173筆，近兩年均價約42.3萬/坪，實登總價1,060~2,270萬
+D區：628筆，均價約45萬/坪；樂居近一年44.72萬（318筆）
+G區：171筆，均價約40~45萬/坪（開價45~48萬/坪）</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>社區整體實登203~227筆成交
-近一年均價約83.5~92萬/坪，近6個月約91.5萬/坪
-最新成交約92.2萬/坪（部分來源顯示區間79.9~110.7萬/坪）</t>
+          <t>樂屋網：227筆成交均價約95.8萬/坪（另載224筆92萬/坪）
+5168：均價約83.5萬／88.4萬/坪
+近一年10筆成交均價約83.5萬/坪，總價區間1,165~2,990萬
+近6個月約91.5萬/坪；最新成交約92.2萬/坪
+（另有來源顯示近一年73.78萬/坪，區間差異大，議價前務必逐筆比對）</t>
         </is>
       </c>
     </row>
@@ -2271,29 +2418,32 @@
           <t>未知待查詢</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>十四張聯開案未來將釋出大量住宅供給，需留意中長期競爭</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>同代銷系列尚有新濠漾II(紐約公園)、新濠漾III(巴黎公園)在銷售</t>
-        </is>
-      </c>
-      <c r="F48" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+          <t>同建商系列案密集推出（II紐約公園約73~78萬/坪、III巴黎公園約82萬/坪）
+新案價高於本案，對本案二手轉售有價格支撐但也形成競爭</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>運校重劃區持續推案，短期供給量偏多</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>本案自身分期供給量大（A~G共約1,000戶以上），二手釋出量多，議價空間與轉手競爭需留意</t>
+          <t>本案自身A~G分期供給量極大（合計逾千戶）
+二手釋出量多，轉手時同社區同質競爭最為激烈</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>社區內約6戶同時銷售中（同社區競品多，可作為議價籌碼）</t>
+          <t>社區內約6戶同時銷售中，可作為議價籌碼
+周邊新建案數未知待查詢</t>
         </is>
       </c>
     </row>
@@ -2313,35 +2463,40 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>約988萬元起，戶價988~2800萬元</t>
+          <t>開價總價1,088~2,800萬
+實登成交總價575~5,730萬（含車位與大坪數戶）</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>約999~2379萬元</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+          <t>開價總價999~2,379萬
+1房（16~18坪）約落在999~1,260萬區間</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>實登成交總價544~3,000萬
+以最小戶21.79坪×66萬計約1,438萬</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>開價約1,200~2,264萬/戶</t>
+          <t>開價總價896~2,535萬（另載1,200~2,264萬/戶）
+1房12~15坪推估約896~1,150萬</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>【看屋範圍推估】以1房20坪、2房23~25坪 × 均價42~46萬/坪計
-1房約840~920萬、2房約970~1,150萬
-（實際開價需向代銷確認，A區實登總價下緣約600萬）</t>
+          <t>廣告訴求總價880萬起
+【看屋範圍推估】1房20坪×約45萬≈900萬；2房23~25坪×約45萬≈1,035~1,125萬
+A區實登總價下緣約600萬</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
           <t>【看屋範圍】1房（1房0廳1衛）最低總價約1,165萬元起
-（早期首購開價約950萬起，現行行情已高於此）</t>
+社區整體成交總價1,165~2,990萬
+（早期首購開價約950萬起，現行行情已明顯高於此）</t>
         </is>
       </c>
     </row>
@@ -2354,33 +2509,38 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>開價75~88萬/坪（近期實登均價約76萬/坪）</t>
+          <t>開價75~88萬/坪
+實際成交約73.7~76萬/坪</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>開價約59~70萬/坪</t>
+          <t>開價59~70萬/坪
+實際成交近一年約66.97萬/坪</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>開價約51~65萬/坪（不同時期資料略有差異）</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+          <t>成交約65.7~67.9萬/坪
+開價曾為51~65萬/坪（早期）</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>開價68~85萬/坪
+實際成交約73.9~79.7萬/坪</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>成交約40~47萬/坪（依分區與屋齡不同）
-G區開價45~48萬/坪</t>
+          <t>各分區成交約40~47萬/坪
+G區開價45~48萬/坪為全案最高</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>約83.5~92萬/坪（近期成交），早期開價約70~85萬/坪</t>
+          <t>近期成交約83.5~92萬/坪（部分來源區間79.9~110.7萬/坪）
+早期開價約70~85萬/坪</t>
         </is>
       </c>
     </row>
@@ -2391,35 +2551,35 @@
           <t>貸款成數與利率試算</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="H52" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢
-（小坪數套房型銀行貸款成數常低於一般住宅，務必先行詢價）</t>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>以總價1,088萬（最小戶）計：貸8成870萬，月付約3.4萬（2.5%）／約3.1萬（新青安1.775%）</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>以總價999萬（1房最小戶）計：貸8成799萬，月付約3.16萬（2.5%）／約2.86萬（新青安1.775%）</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>以總價1,438萬（最小戶21.79坪）計：貸8成1,150萬，月付約4.54萬（2.5%）／新青安僅1,000萬額度內適用</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>以總價896萬（1房最小戶）計：貸8成717萬，月付約2.83萬（2.5%）／約2.57萬（新青安1.775%）</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>以總價900萬（1房20坪）計：貸8成720萬，月付約2.84萬（2.5%）／約2.58萬（新青安1.775%）</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>以總價1,165萬計：貸8成932萬，月付約3.68萬（2.5%）／約3.34萬（新青安1.775%）
+⚠️小坪數套房型銀行貸款成數常低於8成（可能僅6~7成），務必先行詢價</t>
         </is>
       </c>
     </row>
@@ -2430,34 +2590,40 @@
           <t>頭期款與付款方式（工程期款）</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>新成屋：頭期約2成約218萬（以1,088萬計）+ 稅費
+實際付款方式需向代銷確認</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>預售屋：訂簽開約10~15%、工程期款分期、交屋款
+以999萬計頭期約2成200萬，實際成數需向代銷確認</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>已完工社區為一次性買賣
+以1,438萬計頭期約2成288萬 + 稅費</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>預售屋：訂簽開＋工程期款分期＋交屋款
+以896萬計頭期約2成179萬，實際成數需向代銷確認</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>建商宣傳「首付58萬起」（需向代銷確認適用房型與付款條件）</t>
+          <t>建商宣傳「首付58萬起」（需向代銷確認適用房型與付款條件）
+以900萬計一般頭期約2成180萬</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>已完工新古屋，為一次性買賣非工程期款；頭期款依貸款成數而定，未知待查詢</t>
+          <t>已完工成屋，為一次性買賣非工程期款
+以1,165萬、貸8成計頭期約233萬；若僅核貸7成則需350萬</t>
         </is>
       </c>
     </row>
@@ -2468,34 +2634,34 @@
           <t>稅費估算（契稅／印花稅／代書費）</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F54" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="H54" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>以1,088萬計約11~16萬</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>以999萬計約10~15萬</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>以1,438萬計約14~22萬</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>以896萬計約9~13萬</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>以900萬計約9~14萬</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>以1,165萬計約12~17萬（中古屋另有仲介服務費，買方約成交價1~2%約12~23萬）</t>
         </is>
       </c>
     </row>
@@ -2526,14 +2692,17 @@
           <t>未知待查詢</t>
         </is>
       </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="H55" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>B區、D區均為80元/坪/月
+以1房20坪計約1,600元/月；2房25坪約2,000元/月
+A/C/G區未知待查詢</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>約140元/坪/月（24小時飯店式管理）
+以12坪計約1,680元/月；18坪約2,520元/月</t>
         </is>
       </c>
     </row>
@@ -2544,35 +2713,41 @@
           <t>增值潛力／轉手性評估</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="F56" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢</t>
-        </is>
-      </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢（本案量體大、同社區釋出戶數多，轉手時同質競爭激烈，須實地評估）</t>
-        </is>
-      </c>
-      <c r="H56" s="9" t="inlineStr">
-        <is>
-          <t>未知待查詢
-注意：完工年份資料分歧（一說2019年7月、一說2022年），屋齡影響貸款與轉手，請向房仲索取謄本確認</t>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>雙捷交匯與新埔成熟商圈為支撐
+但公設比近40%、高架橋噪音為轉手時的議價點</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>利多：三捷交會、十四張聯開案題材
+風險：預售價已達66~70萬/坪，短期補漲空間需觀察</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>同系列新案價位已達73~82萬/坪，對本案（約66萬）具比價支撐
+但最小戶21.79坪、總價已破1,400萬，非低總價產品</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>利多：頂埔站步行可及、三鶯線通車、土城科技園區就業支撐、四大標章
+風險：661戶大量體＋重劃區供給多，轉手同質競爭激烈</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>利多：基隆捷運保長坑2號站距基地約350公尺（環評中）
+風險：無現有捷運、量體逾千戶、汐止淹水與濕氣印象、鄰近墓地，轉手議價空間需預留</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>利多：北市門牌、內科就業支撐、捷運與機能成熟、租賃需求強
+風險：公設比39%、機械車位、小坪數貸款成數受限
+⚠️完工年份資料分歧（2019年7月／2022年／屋齡約2年三種說法），屋齡直接影響貸款與轉手，務必向房仲索取謄本確認</t>
         </is>
       </c>
     </row>
